--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118325942</v>
+        <v>118326401</v>
       </c>
       <c r="B3" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
+          <t>Ljusmon (Ljusmon), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637806</v>
+        <v>637692</v>
       </c>
       <c r="R3" t="n">
-        <v>7012740</v>
+        <v>7012939</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118326060</v>
+        <v>118325942</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljusmon (Ljusmon), Ång</t>
+          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637736</v>
+        <v>637806</v>
       </c>
       <c r="R4" t="n">
-        <v>7012765</v>
+        <v>7012740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118326401</v>
+        <v>118326060</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637692</v>
+        <v>637736</v>
       </c>
       <c r="R6" t="n">
-        <v>7012939</v>
+        <v>7012765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118511429</v>
+        <v>118511426</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637737</v>
+        <v>637754</v>
       </c>
       <c r="R7" t="n">
-        <v>7012765</v>
+        <v>7012806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118511426</v>
+        <v>118511429</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637754</v>
+        <v>637737</v>
       </c>
       <c r="R8" t="n">
-        <v>7012806</v>
+        <v>7012765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118326208</v>
+        <v>118325942</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637768</v>
+        <v>637806</v>
       </c>
       <c r="R2" t="n">
-        <v>7012813</v>
+        <v>7012740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118326401</v>
+        <v>118326344</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -826,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637692</v>
+        <v>637727</v>
       </c>
       <c r="R3" t="n">
-        <v>7012939</v>
+        <v>7012895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118325942</v>
+        <v>118326060</v>
       </c>
       <c r="B4" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,38 +915,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
+          <t>Ljusmon (Ljusmon), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637806</v>
+        <v>637736</v>
       </c>
       <c r="R4" t="n">
-        <v>7012740</v>
+        <v>7012765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118326344</v>
+        <v>118326208</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1054,19 +1054,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljusmon (Ljusmon), Ång</t>
+          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637727</v>
+        <v>637768</v>
       </c>
       <c r="R5" t="n">
-        <v>7012895</v>
+        <v>7012813</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118326060</v>
+        <v>118326401</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637736</v>
+        <v>637692</v>
       </c>
       <c r="R6" t="n">
-        <v>7012765</v>
+        <v>7012939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118511426</v>
+        <v>118511429</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637754</v>
+        <v>637737</v>
       </c>
       <c r="R7" t="n">
-        <v>7012806</v>
+        <v>7012765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118511429</v>
+        <v>118511426</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637737</v>
+        <v>637754</v>
       </c>
       <c r="R8" t="n">
-        <v>7012765</v>
+        <v>7012806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118325942</v>
+        <v>118326208</v>
       </c>
       <c r="B2" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637806</v>
+        <v>637768</v>
       </c>
       <c r="R2" t="n">
-        <v>7012740</v>
+        <v>7012813</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118326344</v>
+        <v>118325942</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>90531</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljusmon (Ljusmon), Ång</t>
+          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637727</v>
+        <v>637806</v>
       </c>
       <c r="R3" t="n">
-        <v>7012895</v>
+        <v>7012740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
         <v>118326060</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118326208</v>
+        <v>118326344</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,19 +1054,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
+          <t>Ljusmon (Ljusmon), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637768</v>
+        <v>637727</v>
       </c>
       <c r="R5" t="n">
-        <v>7012813</v>
+        <v>7012895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
         <v>118326401</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118511429</v>
+        <v>118511426</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637737</v>
+        <v>637754</v>
       </c>
       <c r="R7" t="n">
-        <v>7012765</v>
+        <v>7012806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118511426</v>
+        <v>118511429</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637754</v>
+        <v>637737</v>
       </c>
       <c r="R8" t="n">
-        <v>7012806</v>
+        <v>7012765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,7 +1510,7 @@
         <v>118511431</v>
       </c>
       <c r="B9" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1251,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118511426</v>
+        <v>118511429</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637754</v>
+        <v>637737</v>
       </c>
       <c r="R7" t="n">
-        <v>7012806</v>
+        <v>7012765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118511429</v>
+        <v>118511426</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637737</v>
+        <v>637754</v>
       </c>
       <c r="R8" t="n">
-        <v>7012765</v>
+        <v>7012806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119937708</v>
+        <v>119937706</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
+        <v>91352</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>2014</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637606</v>
+        <v>637717</v>
       </c>
       <c r="R10" t="n">
-        <v>7012946</v>
+        <v>7012858</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119937706</v>
+        <v>119937708</v>
       </c>
       <c r="B11" t="n">
-        <v>91352</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,21 +1750,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2014</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637717</v>
+        <v>637606</v>
       </c>
       <c r="R11" t="n">
-        <v>7012858</v>
+        <v>7012946</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119937706</v>
+        <v>119937708</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>78171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2014</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637717</v>
+        <v>637606</v>
       </c>
       <c r="R10" t="n">
-        <v>7012858</v>
+        <v>7012946</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119937708</v>
+        <v>119937706</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>91352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,21 +1750,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>2014</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637606</v>
+        <v>637717</v>
       </c>
       <c r="R11" t="n">
-        <v>7012946</v>
+        <v>7012858</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1621,7 +1621,7 @@
         <v>119937706</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>119937708</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>119937707</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119937708</v>
+        <v>119937707</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,21 +1750,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637606</v>
+        <v>637626</v>
       </c>
       <c r="R11" t="n">
-        <v>7012946</v>
+        <v>7012930</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119937707</v>
+        <v>119937708</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637626</v>
+        <v>637606</v>
       </c>
       <c r="R12" t="n">
-        <v>7012930</v>
+        <v>7012946</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119937706</v>
+        <v>119937708</v>
       </c>
       <c r="B10" t="n">
-        <v>91370</v>
+        <v>78187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2014</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637717</v>
+        <v>637606</v>
       </c>
       <c r="R10" t="n">
-        <v>7012858</v>
+        <v>7012946</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119937708</v>
+        <v>119937706</v>
       </c>
       <c r="B12" t="n">
-        <v>78187</v>
+        <v>91370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>2014</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637606</v>
+        <v>637717</v>
       </c>
       <c r="R12" t="n">
-        <v>7012946</v>
+        <v>7012858</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119937708</v>
+        <v>119937707</v>
       </c>
       <c r="B10" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637606</v>
+        <v>637626</v>
       </c>
       <c r="R10" t="n">
-        <v>7012946</v>
+        <v>7012930</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119937707</v>
+        <v>119937706</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>91370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,21 +1750,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>2014</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637626</v>
+        <v>637717</v>
       </c>
       <c r="R11" t="n">
-        <v>7012930</v>
+        <v>7012858</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119937706</v>
+        <v>119937708</v>
       </c>
       <c r="B12" t="n">
-        <v>91370</v>
+        <v>78187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2014</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637717</v>
+        <v>637606</v>
       </c>
       <c r="R12" t="n">
-        <v>7012858</v>
+        <v>7012946</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119937707</v>
+        <v>119937706</v>
       </c>
       <c r="B10" t="n">
-        <v>78278</v>
+        <v>91370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>2014</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637626</v>
+        <v>637717</v>
       </c>
       <c r="R10" t="n">
-        <v>7012930</v>
+        <v>7012858</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119937706</v>
+        <v>119937708</v>
       </c>
       <c r="B11" t="n">
-        <v>91370</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,21 +1750,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2014</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637717</v>
+        <v>637606</v>
       </c>
       <c r="R11" t="n">
-        <v>7012858</v>
+        <v>7012946</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119937708</v>
+        <v>119937707</v>
       </c>
       <c r="B12" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637606</v>
+        <v>637626</v>
       </c>
       <c r="R12" t="n">
-        <v>7012946</v>
+        <v>7012930</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118326208</v>
+        <v>119937708</v>
       </c>
       <c r="B2" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
+          <t>OffersjÃ¶n, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637768</v>
+        <v>637606</v>
       </c>
       <c r="R2" t="n">
-        <v>7012813</v>
+        <v>7012946</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118325942</v>
+        <v>119937706</v>
       </c>
       <c r="B3" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sunnersta-Stormyran (Sunnersta-Stormyran), Ång</t>
+          <t>OffersjÃ¶n, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637806</v>
+        <v>637717</v>
       </c>
       <c r="R3" t="n">
-        <v>7012740</v>
+        <v>7012858</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,66 +885,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118326060</v>
+        <v>118325942</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljusmon (Ljusmon), Ång</t>
+          <t>Sunnersta-Stormyran, Sunnersta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637736</v>
+        <v>637806</v>
       </c>
       <c r="R4" t="n">
-        <v>7012765</v>
+        <v>7012740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,54 +1004,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118326344</v>
+        <v>118511431</v>
       </c>
       <c r="B5" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljusmon (Ljusmon), Ång</t>
+          <t>Följansbodarna, S om, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637727</v>
+        <v>637808</v>
       </c>
       <c r="R5" t="n">
-        <v>7012895</v>
+        <v>7012753</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,21 +1072,11 @@
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,73 +1085,77 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118326401</v>
+        <v>119937707</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ljusmon (Ljusmon), Ång</t>
+          <t>OffersjÃ¶n, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637692</v>
+        <v>637626</v>
       </c>
       <c r="R6" t="n">
-        <v>7012939</v>
+        <v>7012930</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1179,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,62 +1209,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118511431</v>
+        <v>118326060</v>
       </c>
       <c r="B7" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Följansbodarna, S om, Ång</t>
+          <t>Ljusmon, Ljusmon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637808</v>
+        <v>637736</v>
       </c>
       <c r="R7" t="n">
-        <v>7012753</v>
+        <v>7012765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,11 +1293,21 @@
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1337,40 +1316,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>På gammal tall</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SBF Florainventering i Ångermanland 2024</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118511426</v>
+        <v>118326208</v>
       </c>
       <c r="B8" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,28 +1365,16 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Följansbodarna, S om, Ång</t>
+          <t>Sunnersta-Stormyran, Sunnersta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637754</v>
+        <v>637768</v>
       </c>
       <c r="R8" t="n">
-        <v>7012806</v>
+        <v>7012813</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,54 +1404,49 @@
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SBF Florainventering i Ångermanland 2024</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118511429</v>
+        <v>118326344</v>
       </c>
       <c r="B9" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,31 +1473,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Följansbodarna, S om, Ång</t>
+          <t>Ljusmon, Ljusmon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637737</v>
+        <v>637727</v>
       </c>
       <c r="R9" t="n">
-        <v>7012765</v>
+        <v>7012895</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,96 +1515,91 @@
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SBF Florainventering i Ångermanland 2024</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119937706</v>
+        <v>118326401</v>
       </c>
       <c r="B10" t="n">
-        <v>91370</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2014</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>OffersjÃ¶n, Ång</t>
+          <t>Ljusmon, Ljusmon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637717</v>
+        <v>637692</v>
       </c>
       <c r="R10" t="n">
-        <v>7012858</v>
+        <v>7012939</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1692,22 +1623,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,66 +1653,73 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119937708</v>
+        <v>118511426</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>OffersjÃ¶n, Ång</t>
+          <t>Följansbodarna, S om, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637606</v>
+        <v>637754</v>
       </c>
       <c r="R11" t="n">
-        <v>7012946</v>
+        <v>7012806</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,22 +1746,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,75 +1760,92 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119937707</v>
+        <v>118511429</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>OffersjÃ¶n, Ång</t>
+          <t>Följansbodarna, S om, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637626</v>
+        <v>637737</v>
       </c>
       <c r="R12" t="n">
-        <v>7012930</v>
+        <v>7012765</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,22 +1869,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,21 +1883,31 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937708</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118325942</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
           <t>SBF Florainventering i Ångermanland 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118511431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326060</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326208</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326344</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326401</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
           <t>SBF Florainventering i Ångermanland 2024</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118511426</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,8 +1963,26 @@
           <t>SBF Florainventering i Ångermanland 2024</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118511429</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>